--- a/public/sap-reporting/expansion-150-downloads/EXT-SD10-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-SD10-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Rab7f55af4ab9423d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R9c38555a55d845c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R19338995d21f4407"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R3a4b656c0a944f94"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R98e5f3af41ca42ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R7c1b2cbc1c404c95"/>
   </x:sheets>
 </x:workbook>
 </file>
